--- a/artfynd/A 14933-2023 artfynd.xlsx
+++ b/artfynd/A 14933-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14933-2023 artfynd.xlsx
+++ b/artfynd/A 14933-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104418931</v>
+        <v>110058292</v>
       </c>
       <c r="B2" t="n">
-        <v>107952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221049</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nävlinge, Sk</t>
+          <t>Attarps gård VNV 1,2 km, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>426019.454066655</v>
+        <v>426008</v>
       </c>
       <c r="R2" t="n">
-        <v>6215568.998810739</v>
+        <v>6215438</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,24 +764,1066 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Carl-Axel Andersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Carl-Axel Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104419180</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nävlinge, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>425972</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6215488</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Örjan Fritz</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Örjan Fritz</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104419187</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nävlinge, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>426079</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6215618</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-04-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-04-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104419218</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nävlinge, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>426028</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6215573</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-04-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-04-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104419219</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nävlinge, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>426048</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6215588</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-04-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-04-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104418922</v>
+      </c>
+      <c r="B7" t="n">
+        <v>111129</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nävlinge, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>425963</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6215467</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104418927</v>
+      </c>
+      <c r="B8" t="n">
+        <v>111129</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nävlinge, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>425995</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6215559</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104418931</v>
+      </c>
+      <c r="B9" t="n">
+        <v>111129</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nävlinge, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>426020</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6215569</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-04-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-04-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104418934</v>
+      </c>
+      <c r="B10" t="n">
+        <v>111129</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nävlinge, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>425968</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6215475</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104418935</v>
+      </c>
+      <c r="B11" t="n">
+        <v>111129</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nävlinge, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>425972</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6215488</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>116903850</v>
+      </c>
+      <c r="B12" t="n">
+        <v>111129</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1911</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nävlinge kyrka 2,1 km NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>425970</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6215467</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>M-Hlm-0251</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Alsumpkärr (nyligen gallrat)</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Alsumpkärr</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ole Tryggeson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14933-2023 artfynd.xlsx
+++ b/artfynd/A 14933-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110058292</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104419180</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104419187</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104419218</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104419219</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104418922</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104418927</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104418931</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104418934</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,6 +1745,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104418935</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1824,8 +1879,26 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116903850</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>